--- a/diseases/d188/2015-2019.xlsx
+++ b/diseases/d188/2015-2019.xlsx
@@ -439,110 +439,255 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>record_kind</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>country_code</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>country_name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>disease_id</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>disease_name_en</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>disease_name_zh</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>year_month</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>cases</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>weekly_equiv_cases</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>deaths</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>incidence_rate_per_100k</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>incidence_rate_source</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>mortality_rate</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>series_code</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>source_series_code</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>source_system</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>source_label</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>metric_type</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>reporting_basis</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>temporal_granularity</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>geography_key</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>dimension_key</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>mapping_relation</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>comparability</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>aggregation_policy</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>availability_status</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>missing_value_policy</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>definition_version</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>case_definition</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>case_definition_uri</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>quality_status</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>is_selected_series</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>data_layer</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>projection_policy</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>coverage_status</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>loss_risk</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>selected_series_codes</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>available_series_count</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>provenance_note</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
         <is>
           <t>primary_source_scope</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>primary_source_label</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>primary_source_url</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>primary_source_type</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>source_scopes</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>source_labels</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>source_urls</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>source_types</t>
         </is>
@@ -571,97 +716,126 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>2016-01-01</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2016-01</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>31</v>
       </c>
-      <c r="N2" t="n">
-        <v>0.547979797979798</v>
-      </c>
       <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
         <v>0.01525454570268905</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -690,97 +864,126 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>2016-02-01</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>2016-02</t>
         </is>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>16</v>
       </c>
-      <c r="N3" t="n">
-        <v>3.612903225806452</v>
-      </c>
       <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
         <v>0.007873313911065315</v>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -809,97 +1012,126 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>2016-03-01</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>2016-03</t>
         </is>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>24</v>
       </c>
-      <c r="N4" t="n">
-        <v>5.793103448275862</v>
-      </c>
       <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
         <v>0.01180997086659797</v>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -928,97 +1160,126 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>2016-04-01</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>2016-04</t>
         </is>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>27</v>
       </c>
-      <c r="N5" t="n">
-        <v>6.096774193548387</v>
-      </c>
       <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
         <v>0.01328621722492272</v>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -1047,97 +1308,126 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>2016-05-01</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>2016-05</t>
         </is>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>27</v>
       </c>
-      <c r="N6" t="n">
-        <v>6.3</v>
-      </c>
       <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
         <v>0.01328621722492272</v>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -1166,97 +1456,126 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>2016-06-01</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>2016-06</t>
         </is>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>22</v>
       </c>
-      <c r="N7" t="n">
-        <v>4.967741935483871</v>
-      </c>
       <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
         <v>0.01082580662771481</v>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -1285,97 +1604,126 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>2016-07-01</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>2016-07</t>
         </is>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>8</v>
       </c>
-      <c r="N8" t="n">
-        <v>1.866666666666667</v>
-      </c>
       <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
         <v>0.003936656955532658</v>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -1404,97 +1752,126 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>2016-08-01</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>2016-08</t>
         </is>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>18</v>
       </c>
-      <c r="N9" t="n">
-        <v>4.064516129032258</v>
-      </c>
       <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
         <v>0.008857478149948479</v>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -1523,97 +1900,126 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>2016-09-01</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>2016-09</t>
         </is>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>16</v>
       </c>
-      <c r="N10" t="n">
-        <v>3.612903225806452</v>
-      </c>
       <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
         <v>0.007873313911065315</v>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -1642,97 +2048,126 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>2016-10-01</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>2016-10</t>
         </is>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>20</v>
       </c>
-      <c r="N11" t="n">
-        <v>4.666666666666666</v>
-      </c>
       <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
         <v>0.009841642388831643</v>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -1761,97 +2196,126 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>2016-11-01</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>2016-11</t>
         </is>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>31</v>
       </c>
-      <c r="N12" t="n">
-        <v>7</v>
-      </c>
       <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
         <v>0.01525454570268905</v>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -1880,97 +2344,126 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>2016-12-01</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>2016-12</t>
         </is>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>15</v>
       </c>
-      <c r="N13" t="n">
-        <v>3.5</v>
-      </c>
       <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
         <v>0.007381231791623732</v>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -1999,97 +2492,126 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>2018-01-01</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>2018-01</t>
         </is>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>45</v>
       </c>
-      <c r="N14" t="n">
-        <v>0.7954545454545454</v>
-      </c>
       <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
         <v>0.02183329199118631</v>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -2118,97 +2640,126 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>2018-02-01</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>2018-02</t>
         </is>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>31</v>
       </c>
-      <c r="N15" t="n">
-        <v>7</v>
-      </c>
       <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
         <v>0.01504071226059501</v>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -2237,97 +2788,126 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>2018-03-01</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>2018-03</t>
         </is>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>47</v>
       </c>
-      <c r="N16" t="n">
-        <v>11.75</v>
-      </c>
       <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
         <v>0.02280366052412792</v>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -2356,97 +2936,126 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>2018-04-01</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>2018-04</t>
         </is>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>35</v>
       </c>
-      <c r="N17" t="n">
-        <v>7.903225806451614</v>
-      </c>
       <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
         <v>0.01698144932647824</v>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -2475,97 +3084,126 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>2018-05-01</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>2018-05</t>
         </is>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>28</v>
       </c>
-      <c r="N18" t="n">
-        <v>6.533333333333333</v>
-      </c>
       <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
         <v>0.01358515946118259</v>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -2594,97 +3232,126 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>2018-06-01</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>2018-06</t>
         </is>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>32</v>
       </c>
-      <c r="N19" t="n">
-        <v>7.225806451612903</v>
-      </c>
       <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
         <v>0.01552589652706582</v>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -2713,97 +3380,126 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>2018-07-01</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>2018-07</t>
         </is>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>11</v>
       </c>
-      <c r="N20" t="n">
-        <v>2.566666666666666</v>
-      </c>
       <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
         <v>0.005337026931178875</v>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -2832,97 +3528,126 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>2018-08-01</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>2018-08</t>
         </is>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>64</v>
       </c>
-      <c r="N21" t="n">
-        <v>14.45161290322581</v>
-      </c>
       <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
         <v>0.03105179305413164</v>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -2951,97 +3676,126 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>2018-09-01</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>2018-09</t>
         </is>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>29</v>
       </c>
-      <c r="N22" t="n">
-        <v>6.548387096774193</v>
-      </c>
       <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
         <v>0.0140703437276534</v>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -3070,97 +3824,126 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>2018-10-01</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>2018-10</t>
         </is>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>31</v>
       </c>
-      <c r="N23" t="n">
-        <v>7.233333333333334</v>
-      </c>
       <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
         <v>0.01504071226059501</v>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -3189,97 +3972,126 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>2018-11-01</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>2018-11</t>
         </is>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>15</v>
       </c>
-      <c r="N24" t="n">
-        <v>3.387096774193548</v>
-      </c>
       <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
         <v>0.007277763997062103</v>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -3308,97 +4120,126 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>2018-12-01</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>2018-12</t>
         </is>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>30</v>
       </c>
-      <c r="N25" t="n">
-        <v>7</v>
-      </c>
       <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
         <v>0.01455552799412421</v>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC25" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -3427,97 +4268,126 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>2019-01-01</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>2019-01</t>
         </is>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>56</v>
       </c>
-      <c r="N26" t="n">
-        <v>12.64516129032258</v>
-      </c>
       <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
         <v>0.02699374609613492</v>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -3546,97 +4416,126 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>2019-02-01</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>2019-02</t>
         </is>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>67</v>
       </c>
-      <c r="N27" t="n">
-        <v>15.12903225806452</v>
-      </c>
       <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
         <v>0.03229608907930427</v>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC27" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -3665,97 +4564,126 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>2019-03-01</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>2019-03</t>
         </is>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>80</v>
       </c>
-      <c r="N28" t="n">
-        <v>20</v>
-      </c>
       <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
         <v>0.03856249442304988</v>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC28" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -3784,97 +4712,126 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>2019-04-01</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>2019-04</t>
         </is>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>95</v>
       </c>
-      <c r="N29" t="n">
-        <v>21.45161290322581</v>
-      </c>
       <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
         <v>0.04579296212737173</v>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC29" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -3903,97 +4860,126 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>2019-05-01</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>2019-05</t>
         </is>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>91</v>
       </c>
-      <c r="N30" t="n">
-        <v>21.23333333333333</v>
-      </c>
       <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
         <v>0.04386483740621924</v>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC30" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -4022,97 +5008,126 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>2019-06-01</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>2019-06</t>
         </is>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>82</v>
       </c>
-      <c r="N31" t="n">
-        <v>18.51612903225806</v>
-      </c>
       <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
         <v>0.03952655678362613</v>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC31" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -4141,97 +5156,126 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>2019-07-01</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>2019-07</t>
         </is>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>57</v>
       </c>
-      <c r="N32" t="n">
-        <v>13.3</v>
-      </c>
       <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
         <v>0.02747577727642304</v>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC32" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -4260,97 +5304,126 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>2019-08-01</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>2019-08</t>
         </is>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>44</v>
       </c>
-      <c r="N33" t="n">
-        <v>9.935483870967742</v>
-      </c>
       <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
         <v>0.02120937193267743</v>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC33" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -4379,97 +5452,126 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>2019-09-01</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>2019-09</t>
         </is>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>52</v>
       </c>
-      <c r="N34" t="n">
-        <v>11.74193548387097</v>
-      </c>
       <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
         <v>0.02506562137498242</v>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr"/>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC34" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -4498,97 +5600,126 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>2019-10-01</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>2019-10</t>
         </is>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>55</v>
       </c>
-      <c r="N35" t="n">
-        <v>12.83333333333333</v>
-      </c>
       <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
         <v>0.02651171491584679</v>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr"/>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV35" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA35" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC35" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -4617,97 +5748,126 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>2019-11-01</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>2019-11</t>
         </is>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>50</v>
       </c>
-      <c r="N36" t="n">
-        <v>11.29032258064516</v>
-      </c>
       <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
         <v>0.02410155901440617</v>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV36" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA36" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC36" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -4736,97 +5896,126 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>D188</t>
-        </is>
-      </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
+          <t>Work-related cancer</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
           <t>职业相关癌症</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>2019-12-01</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>2019-12</t>
         </is>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>62</v>
       </c>
-      <c r="N37" t="n">
-        <v>14.46666666666667</v>
-      </c>
       <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
         <v>0.02988593317786365</v>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV37" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA37" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC37" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -4944,7 +6133,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>record_count</t>
+          <t>projection_record_count</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -4954,27 +6143,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>schema_version</t>
+          <t>record_count</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>total_cases</t>
+          <t>schema_version</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1444</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>total_deaths</t>
+          <t>source_observation_count</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -4984,22 +6173,64 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>window_end</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2019-12-31</t>
-        </is>
+          <t>source_series_count</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>total_basis</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>total_cases</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>total_deaths</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2019-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>window_start</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2015-01-01</t>
         </is>
